--- a/Cennik_v2.xlsx
+++ b/Cennik_v2.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Rovná strecha Juh — balastová konštrukcia 15°</t>
+          <t>Rovná strecha Juh — balastová konštrukcia 13°</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
